--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -460,10 +460,10 @@
         <v>0.5862000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.008</v>
+        <v>0.5454</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0386</v>
+        <v>0.4928</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         <v>0.5841</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5642</v>
+        <v>0.5059</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5401</v>
+        <v>0.4527</v>
       </c>
     </row>
     <row r="4">
@@ -492,10 +492,10 @@
         <v>0.6127</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6109</v>
+        <v>0.5014</v>
       </c>
       <c r="D4" t="n">
-        <v>0.819</v>
+        <v>0.7776</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         <v>0.47</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4405</v>
+        <v>0.5542</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6637</v>
+        <v>0.6932</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         <v>0.5458</v>
       </c>
       <c r="C6" t="n">
-        <v>0.533</v>
+        <v>0.334</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.2743</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +540,10 @@
         <v>0.6634</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7133</v>
+        <v>0.5775</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7245</v>
+        <v>0.5901999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -556,10 +556,10 @@
         <v>0.3567</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6445</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4142</v>
+        <v>0.4422</v>
       </c>
     </row>
     <row r="9">
@@ -572,10 +572,10 @@
         <v>0.5331</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.4694</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0774</v>
+        <v>0.4419</v>
       </c>
     </row>
     <row r="10">
@@ -588,10 +588,10 @@
         <v>0.5507</v>
       </c>
       <c r="C10" t="n">
-        <v>0.646</v>
+        <v>0.6186</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5395</v>
+        <v>0.6574</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         <v>0.5208</v>
       </c>
       <c r="C11" t="n">
-        <v>0.014</v>
+        <v>0.6106</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0166</v>
+        <v>0.6385999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -620,10 +620,10 @@
         <v>0.5424</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4238</v>
+        <v>0.5286</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4315</v>
+        <v>0.5461</v>
       </c>
     </row>
   </sheetData>
